--- a/Models/Верблюды/results/Верблюды - Результаты прогнозов SARIMA.xlsx
+++ b/Models/Верблюды/results/Верблюды - Результаты прогнозов SARIMA.xlsx
@@ -488,12 +488,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -513,11 +513,11 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>4.073463452755631e+17</v>
+        <v>1.567678162812935e+17</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>[-0.0, 0.0, -0.0]</t>
+          <t>[0.0, -0.0, -0.0]</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -534,12 +534,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -559,11 +559,11 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>2.970188874197312e+17</v>
+        <v>1.641029290716528e+17</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>[0.0, -0.0, -0.0]</t>
+          <t>[-0.0, -0.0, -0.0]</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -580,12 +580,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -605,11 +605,11 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>1.251961128948378e+17</v>
+        <v>3.013838969292737e+17</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>[-0.0, -0.0, -0.0]</t>
+          <t>[-0.0, -0.0, 0.0]</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -626,12 +626,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -651,11 +651,11 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1.102837260518193e+18</v>
+        <v>3.110096557184541e+17</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>[-0.0, -0.0, 0.0]</t>
+          <t>[-0.0, 0.0, -0.0]</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -672,12 +672,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -697,11 +697,11 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>1.083282317046571e+18</v>
+        <v>2.88628032405297e+17</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>[-0.0, 0.0, -0.0]</t>
+          <t>[0.0, -0.0, 0.0]</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -743,11 +743,11 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>7.366425850061787e+17</v>
+        <v>1.687240850186388e+17</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>[0.0, -0.0, 0.0]</t>
+          <t>[-0.0, 0.0, -0.0]</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -764,12 +764,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -789,11 +789,11 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>1.168405523694244e+17</v>
+        <v>1.217107107019012e+17</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, -0.0]</t>
+          <t>[0.0, -0.0, -0.0]</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -810,12 +810,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -835,11 +835,11 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>1.567678162812935e+17</v>
+        <v>1.694643351317062e+17</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>[0.0, -0.0, -0.0]</t>
+          <t>[-0.0, -0.0, -0.0]</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -856,12 +856,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -881,11 +881,11 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1.641029290716528e+17</v>
+        <v>3.412263797400769e+17</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>[-0.0, -0.0, -0.0]</t>
+          <t>[-0.0, -0.0, 0.0]</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -902,12 +902,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -927,11 +927,11 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>3.013838969292737e+17</v>
+        <v>3.199702697555473e+17</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>[-0.0, -0.0, 0.0]</t>
+          <t>[-0.0, 0.0, -0.0]</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -948,17 +948,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(2, 0, 0)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -967,22 +967,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>16.2</v>
+        <v>0.51</v>
       </c>
       <c r="G12" t="n">
-        <v>13.49</v>
+        <v>0.36</v>
       </c>
       <c r="H12" t="n">
-        <v>7.47</v>
+        <v>0.65</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>[112.12, 65.68, 364.84]</t>
+          <t>[5.69, 49.66, 62.14]</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>[119.5, 72.6, 391.0]</t>
+          <t>[5.7, 49.87, 63.0]</t>
         </is>
       </c>
     </row>
@@ -994,17 +994,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(2, 0, 0)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1013,22 +1013,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>14.81</v>
+        <v>1.32</v>
       </c>
       <c r="G13" t="n">
-        <v>13.04</v>
+        <v>1.05</v>
       </c>
       <c r="H13" t="n">
-        <v>7.5</v>
+        <v>1.03</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>[66.3, 368.29, 115.99]</t>
+          <t>[49.68, 62.16, 152.18]</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>[72.6, 391.0, 126.1]</t>
+          <t>[49.87, 63.0, 154.3]</t>
         </is>
       </c>
     </row>
@@ -1040,17 +1040,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(2, 0, 0)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1059,22 +1059,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>13.13</v>
+        <v>2.71</v>
       </c>
       <c r="G14" t="n">
-        <v>12.59</v>
+        <v>2.31</v>
       </c>
       <c r="H14" t="n">
-        <v>5.45</v>
+        <v>1.1</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>[373.53, 117.65, 217.25]</t>
+          <t>[62.21, 152.33, 534.22]</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>[391.0, 126.1, 229.1]</t>
+          <t>[63.0, 154.3, 538.4]</t>
         </is>
       </c>
     </row>
@@ -1086,17 +1086,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(2, 0, 0)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1105,22 +1105,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>7.28</v>
+        <v>5.66</v>
       </c>
       <c r="G15" t="n">
-        <v>6.09</v>
+        <v>4.48</v>
       </c>
       <c r="H15" t="n">
-        <v>5.3</v>
+        <v>2.91</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>[118.59, 219.0, 11.53]</t>
+          <t>[152.7, 535.87, 119.97]</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>[126.1, 229.1, 12.2]</t>
+          <t>[154.3, 538.4, 129.3]</t>
         </is>
       </c>
     </row>
@@ -1132,17 +1132,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(2, 0, 0)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1151,22 +1151,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.66</v>
+        <v>5.95</v>
       </c>
       <c r="G16" t="n">
-        <v>3.65</v>
+        <v>5.08</v>
       </c>
       <c r="H16" t="n">
-        <v>6.56</v>
+        <v>4.46</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>[221.58, 11.66, 21.21]</t>
+          <t>[536.95, 120.28, 72.84]</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>[229.1, 12.2, 24.1]</t>
+          <t>[538.4, 129.3, 77.6]</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>(0, 1, 3)</t>
+          <t>(2, 0, 0)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1197,22 +1197,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.75</v>
+        <v>12.76</v>
       </c>
       <c r="G17" t="n">
-        <v>1.25</v>
+        <v>11.11</v>
       </c>
       <c r="H17" t="n">
-        <v>7.13</v>
+        <v>5.93</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>[11.7, 21.12, 5.42]</t>
+          <t>[120.34, 72.88, 391.86]</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>[12.2, 24.1, 5.7]</t>
+          <t>[129.3, 77.6, 411.5]</t>
         </is>
       </c>
     </row>
@@ -1224,17 +1224,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>(0, 1, 3)</t>
+          <t>(2, 0, 0)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1243,22 +1243,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.14</v>
+        <v>7.67</v>
       </c>
       <c r="G18" t="n">
-        <v>1.82</v>
+        <v>5.82</v>
       </c>
       <c r="H18" t="n">
-        <v>6.8</v>
+        <v>2.89</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>[21.31, 5.47, 47.43]</t>
+          <t>[73.91, 398.79, 127.05]</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>[24.1, 5.7, 49.87]</t>
+          <t>[77.6, 411.5, 128.1]</t>
         </is>
       </c>
     </row>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1289,22 +1289,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0.51</v>
+        <v>5.7</v>
       </c>
       <c r="G19" t="n">
-        <v>0.36</v>
+        <v>4.56</v>
       </c>
       <c r="H19" t="n">
-        <v>0.65</v>
+        <v>1.45</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>[5.69, 49.66, 62.14]</t>
+          <t>[402.64, 128.58, 231.37]</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>[5.7, 49.87, 63.0]</t>
+          <t>[411.5, 128.1, 235.7]</t>
         </is>
       </c>
     </row>
@@ -1316,12 +1316,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1335,22 +1335,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.32</v>
+        <v>1.87</v>
       </c>
       <c r="G20" t="n">
-        <v>1.05</v>
+        <v>1.4</v>
       </c>
       <c r="H20" t="n">
-        <v>1.03</v>
+        <v>0.97</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>[49.68, 62.16, 152.18]</t>
+          <t>[129.15, 232.63, 12.3]</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>[49.87, 63.0, 154.3]</t>
+          <t>[128.1, 235.7, 12.2]</t>
         </is>
       </c>
     </row>
@@ -1362,12 +1362,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1381,22 +1381,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.71</v>
+        <v>2.07</v>
       </c>
       <c r="G21" t="n">
-        <v>2.31</v>
+        <v>1.5</v>
       </c>
       <c r="H21" t="n">
-        <v>1.1</v>
+        <v>1.98</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>[62.21, 152.33, 534.22]</t>
+          <t>[232.25, 12.27, 24.2]</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>[63.0, 154.3, 538.4]</t>
+          <t>[235.7, 12.2, 25.17]</t>
         </is>
       </c>
     </row>
@@ -1408,12 +1408,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1423,26 +1423,26 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>(2, 1, 0, 12)</t>
+          <t>(1, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>6.29</v>
+        <v>15.54</v>
       </c>
       <c r="G22" t="n">
-        <v>5.88</v>
+        <v>13.06</v>
       </c>
       <c r="H22" t="n">
-        <v>39.94</v>
+        <v>101.32</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>[15.32, 12.25, 21.41]</t>
+          <t>[0.25, 19.97, 3.75]</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>[18.9, 17.4, 12.5]</t>
+          <t>[24.0, 7.7, 6.9]</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1469,26 +1469,26 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>(2, 1, 0, 12)</t>
+          <t>(1, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>8.84</v>
+        <v>7.14</v>
       </c>
       <c r="G23" t="n">
-        <v>8.470000000000001</v>
+        <v>5.37</v>
       </c>
       <c r="H23" t="n">
-        <v>56.66</v>
+        <v>75.12</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>[12.25, 21.4, 5.06]</t>
+          <t>[19.7, 5.21, 2.97]</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>[17.4, 12.5, 16.4]</t>
+          <t>[7.7, 6.9, 5.4]</t>
         </is>
       </c>
     </row>
@@ -1500,12 +1500,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1515,26 +1515,26 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>(2, 1, 0, 12)</t>
+          <t>(1, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>8.619999999999999</v>
+        <v>10.23</v>
       </c>
       <c r="G24" t="n">
-        <v>8.050000000000001</v>
+        <v>7.23</v>
       </c>
       <c r="H24" t="n">
-        <v>58</v>
+        <v>70.01000000000001</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>[21.4, 5.05, 7.7]</t>
+          <t>[5.14, 2.92, 30.06]</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>[12.5, 16.4, 11.6]</t>
+          <t>[6.9, 5.4, 12.6]</t>
         </is>
       </c>
     </row>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1561,26 +1561,26 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>(2, 1, 0, 12)</t>
+          <t>(1, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>7.36</v>
+        <v>11.33</v>
       </c>
       <c r="G25" t="n">
-        <v>6.5</v>
+        <v>9.5</v>
       </c>
       <c r="H25" t="n">
-        <v>42.8</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>[5.04, 7.69, 12.45]</t>
+          <t>[2.9, 30.13, 14.14]</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>[16.4, 11.6, 16.7]</t>
+          <t>[5.4, 12.6, 22.6]</t>
         </is>
       </c>
     </row>
@@ -1592,12 +1592,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1607,26 +1607,26 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>(2, 1, 0, 12)</t>
+          <t>(1, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>5.5</v>
+        <v>12.6</v>
       </c>
       <c r="G26" t="n">
-        <v>5.25</v>
+        <v>11.97</v>
       </c>
       <c r="H26" t="n">
-        <v>35.82</v>
+        <v>76.20999999999999</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>[7.69, 12.45, 8.11]</t>
+          <t>[30.08, 14.15, 9.03]</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>[11.6, 16.7, 15.7]</t>
+          <t>[12.6, 22.6, 19.0]</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1657,22 +1657,22 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>15.08</v>
+        <v>12.88</v>
       </c>
       <c r="G27" t="n">
-        <v>13.02</v>
+        <v>12.18</v>
       </c>
       <c r="H27" t="n">
-        <v>64.67</v>
+        <v>103.4</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>[23.26, 6.92, 0.29]</t>
+          <t>[14.13, 8.97, 26.24]</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>[16.7, 15.7, 24.0]</t>
+          <t>[22.6, 19.0, 8.2]</t>
         </is>
       </c>
     </row>
@@ -1684,12 +1684,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1703,22 +1703,22 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>16.24</v>
+        <v>13.72</v>
       </c>
       <c r="G28" t="n">
-        <v>14.93</v>
+        <v>13.26</v>
       </c>
       <c r="H28" t="n">
-        <v>104.75</v>
+        <v>123.55</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>[6.91, 0.27, 19.97]</t>
+          <t>[8.9, 26.37, 0.5]</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>[15.7, 24.0, 7.7]</t>
+          <t>[19.0, 8.2, 12.0]</t>
         </is>
       </c>
     </row>
@@ -1730,12 +1730,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1749,22 +1749,22 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>15.54</v>
+        <v>24.77</v>
       </c>
       <c r="G29" t="n">
-        <v>13.06</v>
+        <v>22.27</v>
       </c>
       <c r="H29" t="n">
-        <v>101.32</v>
+        <v>136.36</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>[0.25, 19.97, 3.75]</t>
+          <t>[26.41, 0.5, 3.6]</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>[24.0, 7.7, 6.9]</t>
+          <t>[8.2, 12.0, 40.7]</t>
         </is>
       </c>
     </row>
@@ -1776,12 +1776,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1795,22 +1795,22 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>7.14</v>
+        <v>26.86</v>
       </c>
       <c r="G30" t="n">
-        <v>5.37</v>
+        <v>24.73</v>
       </c>
       <c r="H30" t="n">
-        <v>75.12</v>
+        <v>82.86</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>[19.7, 5.21, 2.97]</t>
+          <t>[0.49, 3.58, 16.02]</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>[7.7, 6.9, 5.4]</t>
+          <t>[12.0, 40.7, 41.6]</t>
         </is>
       </c>
     </row>
@@ -1822,12 +1822,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1841,22 +1841,22 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>10.23</v>
+        <v>22.46</v>
       </c>
       <c r="G31" t="n">
-        <v>7.23</v>
+        <v>17.65</v>
       </c>
       <c r="H31" t="n">
-        <v>70.01000000000001</v>
+        <v>43.75</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>[5.14, 2.92, 30.06]</t>
+          <t>[5.07, 57.13, 26.31]</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>[6.9, 5.4, 12.6]</t>
+          <t>[40.7, 41.6, 28.1]</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1887,22 +1887,22 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>128.31</v>
+        <v>47.34</v>
       </c>
       <c r="G32" t="n">
-        <v>102.81</v>
+        <v>45.2</v>
       </c>
       <c r="H32" t="n">
-        <v>24.63</v>
+        <v>12.56</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>[298.54, 216.37, 517.67]</t>
+          <t>[164.29, 770.89, 773.96]</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>[323.81, 423.76, 441.9]</t>
+          <t>[133.5, 730.34, 709.68]</t>
         </is>
       </c>
     </row>
@@ -1914,12 +1914,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1933,22 +1933,22 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>124.1</v>
+        <v>39.85</v>
       </c>
       <c r="G33" t="n">
-        <v>100.04</v>
+        <v>34.3</v>
       </c>
       <c r="H33" t="n">
-        <v>25.13</v>
+        <v>5.21</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>[224.42, 518.59, 195.0]</t>
+          <t>[716.11, 771.75, 564.2]</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>[423.76, 441.9, 219.1]</t>
+          <t>[730.34, 709.68, 537.6]</t>
         </is>
       </c>
     </row>
@@ -1960,12 +1960,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1979,22 +1979,22 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>154.14</v>
+        <v>223.69</v>
       </c>
       <c r="G34" t="n">
-        <v>105.89</v>
+        <v>158.24</v>
       </c>
       <c r="H34" t="n">
-        <v>25.43</v>
+        <v>18.46</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>[706.11, 197.08, 456.24]</t>
+          <t>[777.06, 564.35, 1310.88]</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>[441.9, 219.1, 487.69]</t>
+          <t>[709.68, 537.6, 930.28]</t>
         </is>
       </c>
     </row>
@@ -2006,41 +2006,41 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>(0, 0, 3)</t>
+          <t>(0, 0, 1)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>54.09</v>
+        <v>219.71</v>
       </c>
       <c r="G35" t="n">
-        <v>49.94</v>
+        <v>138.95</v>
       </c>
       <c r="H35" t="n">
-        <v>16.26</v>
+        <v>17.09</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>[148.8, 429.59, 468.32]</t>
+          <t>[546.74, 1309.66, 350.43]</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>[219.1, 487.69, 446.9]</t>
+          <t>[537.6, 930.28, 322.1]</t>
         </is>
       </c>
     </row>
@@ -2052,12 +2052,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2071,22 +2071,22 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>3.78</v>
+        <v>225.98</v>
       </c>
       <c r="G36" t="n">
-        <v>3.12</v>
+        <v>173.1</v>
       </c>
       <c r="H36" t="n">
-        <v>1.09</v>
+        <v>30.12</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>[492.66, 446.77, 187.16]</t>
+          <t>[1301.98, 350.35, 405.87]</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>[487.69, 446.9, 191.43]</t>
+          <t>[930.28, 322.1, 286.54]</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2113,26 +2113,26 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>17.26</v>
+        <v>98.31</v>
       </c>
       <c r="G37" t="n">
-        <v>11.82</v>
+        <v>67.76000000000001</v>
       </c>
       <c r="H37" t="n">
-        <v>8.24</v>
+        <v>22.42</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>[445.26, 187.15, 163.03]</t>
+          <t>[313.36, 454.51, 473.97]</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>[446.9, 191.43, 133.5]</t>
+          <t>[322.1, 286.54, 447.4]</t>
         </is>
       </c>
     </row>
@@ -2144,12 +2144,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2159,26 +2159,26 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>28.91</v>
+        <v>102.37</v>
       </c>
       <c r="G38" t="n">
-        <v>24.61</v>
+        <v>76.94</v>
       </c>
       <c r="H38" t="n">
-        <v>9.92</v>
+        <v>26.01</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>[187.36, 163.03, 770.57]</t>
+          <t>[458.92, 474.13, 235.08]</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>[191.43, 133.5, 730.34]</t>
+          <t>[286.54, 447.4, 266.8]</t>
         </is>
       </c>
     </row>
@@ -2190,12 +2190,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2209,22 +2209,22 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>47.34</v>
+        <v>24.29</v>
       </c>
       <c r="G39" t="n">
-        <v>45.2</v>
+        <v>19.65</v>
       </c>
       <c r="H39" t="n">
-        <v>12.56</v>
+        <v>6.23</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>[164.29, 770.89, 773.96]</t>
+          <t>[443.12, 228.12, 512.54]</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>[133.5, 730.34, 709.68]</t>
+          <t>[447.4, 266.8, 496.55]</t>
         </is>
       </c>
     </row>
@@ -2236,12 +2236,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2255,22 +2255,22 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>39.85</v>
+        <v>123.89</v>
       </c>
       <c r="G40" t="n">
-        <v>34.3</v>
+        <v>88.22</v>
       </c>
       <c r="H40" t="n">
-        <v>5.21</v>
+        <v>16.03</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>[716.11, 771.75, 564.2]</t>
+          <t>[228.72, 512.57, 477.43]</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>[730.34, 709.68, 537.6]</t>
+          <t>[266.8, 496.55, 688.0]</t>
         </is>
       </c>
     </row>
@@ -2282,12 +2282,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2301,22 +2301,22 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>223.69</v>
+        <v>123.69</v>
       </c>
       <c r="G41" t="n">
-        <v>158.24</v>
+        <v>87.31</v>
       </c>
       <c r="H41" t="n">
-        <v>18.46</v>
+        <v>14.53</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>[777.06, 564.35, 1310.88]</t>
+          <t>[539.02, 478.24, 203.02]</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>[709.68, 537.6, 930.28]</t>
+          <t>[496.55, 688.0, 212.7]</t>
         </is>
       </c>
     </row>
@@ -2328,12 +2328,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2343,26 +2343,26 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(1, 1, 2, 12)</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="H42" t="n">
-        <v>2.477090280608983e+18</v>
+        <v>8.77902098391636e+19</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>[-0.0, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, 0.4]</t>
         </is>
       </c>
     </row>
@@ -2374,12 +2374,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2389,26 +2389,26 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(1, 1, 2, 12)</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>0.45</v>
+        <v>0.23</v>
       </c>
       <c r="G43" t="n">
-        <v>0.26</v>
+        <v>0.15</v>
       </c>
       <c r="H43" t="n">
-        <v>2.531484946677709e+18</v>
+        <v>4.334435790278415e+21</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.02]</t>
+          <t>[0.0, 0.0, 0.05]</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.8]</t>
+          <t>[0.0, 0.4, 0.0]</t>
         </is>
       </c>
     </row>
@@ -2420,12 +2420,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2435,26 +2435,26 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(1, 1, 2, 12)</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>0.45</v>
+        <v>0.24</v>
       </c>
       <c r="G44" t="n">
-        <v>0.26</v>
+        <v>0.18</v>
       </c>
       <c r="H44" t="n">
-        <v>1.772536164644595e+18</v>
+        <v>1.139127116880879e+22</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>[0.0, 0.02, -0.0]</t>
+          <t>[0.0, 0.05, 0.09]</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>[0.0, 0.8, 0.0]</t>
+          <t>[0.4, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -2466,12 +2466,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2485,22 +2485,22 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>0.45</v>
+        <v>0.1</v>
       </c>
       <c r="G45" t="n">
-        <v>0.26</v>
+        <v>0.08</v>
       </c>
       <c r="H45" t="n">
-        <v>3.528672454133328e+18</v>
+        <v>1.894012947165993e+22</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>[0.02, -0.0, 0.0]</t>
+          <t>[0.08, 0.16, -0.0]</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>[0.8, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -2512,12 +2512,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2531,22 +2531,22 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>0.29</v>
+        <v>0.41</v>
       </c>
       <c r="G46" t="n">
-        <v>0.17</v>
+        <v>0.28</v>
       </c>
       <c r="H46" t="n">
-        <v>2.85979577632878e+18</v>
+        <v>1.006255469875135e+22</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>[-0.0, 0.0, 0.0]</t>
+          <t>[0.13, -0.0, 0.0]</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.5]</t>
+          <t>[0.0, 0.0, 0.7]</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2577,22 +2577,22 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>0.29</v>
+        <v>0.4</v>
       </c>
       <c r="G47" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="H47" t="n">
-        <v>1.121308192960549e+19</v>
+        <v>2.484415204096068e+17</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[-0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>[0.0, 0.5, 0.0]</t>
+          <t>[0.0, 0.7, 0.0]</t>
         </is>
       </c>
     </row>
@@ -2604,12 +2604,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2623,22 +2623,22 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>0.29</v>
+        <v>1.72</v>
       </c>
       <c r="G48" t="n">
-        <v>0.17</v>
+        <v>1.2</v>
       </c>
       <c r="H48" t="n">
-        <v>1.167678659893624e+19</v>
+        <v>2.176108389888071e+17</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, 0.01]</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>[0.5, 0.0, 0.0]</t>
+          <t>[0.7, 0.0, 2.9]</t>
         </is>
       </c>
     </row>
@@ -2650,12 +2650,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2669,22 +2669,22 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>0.23</v>
+        <v>1.75</v>
       </c>
       <c r="G49" t="n">
-        <v>0.13</v>
+        <v>1.26</v>
       </c>
       <c r="H49" t="n">
-        <v>8.77902098391636e+19</v>
+        <v>2.585553015986962e+17</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, 0.01, -0.0]</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.4]</t>
+          <t>[0.0, 2.9, 0.9]</t>
         </is>
       </c>
     </row>
@@ -2696,12 +2696,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2715,22 +2715,22 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>0.23</v>
+        <v>1.75</v>
       </c>
       <c r="G50" t="n">
-        <v>0.15</v>
+        <v>1.26</v>
       </c>
       <c r="H50" t="n">
-        <v>4.334435790278415e+21</v>
+        <v>1.065567459994639e+18</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.05]</t>
+          <t>[0.01, -0.0, 0.0]</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>[0.0, 0.4, 0.0]</t>
+          <t>[2.9, 0.9, 0.0]</t>
         </is>
       </c>
     </row>
@@ -2742,12 +2742,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2757,26 +2757,26 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>(1, 1, 2, 12)</t>
+          <t>(0, 1, 2, 12)</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>0.24</v>
+        <v>0.62</v>
       </c>
       <c r="G51" t="n">
-        <v>0.18</v>
+        <v>0.5</v>
       </c>
       <c r="H51" t="n">
-        <v>1.139127116880879e+22</v>
+        <v>1.846474125418032e+18</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>[0.0, 0.05, 0.09]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>[0.4, 0.0, 0.0]</t>
+          <t>[0.9, 0.0, 0.6]</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2834,12 +2834,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2880,12 +2880,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3110,12 +3110,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3248,12 +3248,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3340,12 +3340,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3386,12 +3386,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3478,12 +3478,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3503,11 +3503,11 @@
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>133.33</v>
+        <v>0</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>[-0.0, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3570,12 +3570,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3662,12 +3662,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3708,12 +3708,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3800,12 +3800,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4030,12 +4030,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4076,12 +4076,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4168,12 +4168,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4187,22 +4187,22 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>1.3</v>
+        <v>3.12</v>
       </c>
       <c r="G82" t="n">
-        <v>1.25</v>
+        <v>3.09</v>
       </c>
       <c r="H82" t="n">
-        <v>2.03</v>
+        <v>13.21</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>[108.21, 31.59, 57.56]</t>
+          <t>[10.73, 95.97, 22.63]</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>[109.8, 32.3, 59.0]</t>
+          <t>[14.2, 98.5, 25.9]</t>
         </is>
       </c>
     </row>
@@ -4214,12 +4214,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4233,22 +4233,22 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>0.96</v>
+        <v>2.72</v>
       </c>
       <c r="G83" t="n">
-        <v>0.86</v>
+        <v>2.68</v>
       </c>
       <c r="H83" t="n">
-        <v>2.36</v>
+        <v>7.3</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>[31.59, 57.56, 16.68]</t>
+          <t>[95.97, 22.63, 31.35]</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>[32.3, 59.0, 17.1]</t>
+          <t>[98.5, 25.9, 33.6]</t>
         </is>
       </c>
     </row>
@@ -4260,12 +4260,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4279,22 +4279,22 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>0.87</v>
+        <v>2.29</v>
       </c>
       <c r="G84" t="n">
-        <v>0.62</v>
+        <v>1.84</v>
       </c>
       <c r="H84" t="n">
-        <v>1.66</v>
+        <v>6.5</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>[57.56, 16.68, 14.41]</t>
+          <t>[22.63, 31.35, 5.81]</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>[59.0, 17.1, 14.4]</t>
+          <t>[25.9, 33.6, 5.8]</t>
         </is>
       </c>
     </row>
@@ -4306,12 +4306,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4325,22 +4325,22 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>4.46</v>
+        <v>1.3</v>
       </c>
       <c r="G85" t="n">
-        <v>2.72</v>
+        <v>0.75</v>
       </c>
       <c r="H85" t="n">
-        <v>11.68</v>
+        <v>2.29</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>[16.68, 14.41, 16.02]</t>
+          <t>[31.35, 5.81, 109.8]</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>[17.1, 14.4, 23.74]</t>
+          <t>[33.6, 5.8, 109.8]</t>
         </is>
       </c>
     </row>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4371,22 +4371,22 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>4.48</v>
+        <v>2.37</v>
       </c>
       <c r="G86" t="n">
-        <v>2.84</v>
+        <v>1.37</v>
       </c>
       <c r="H86" t="n">
-        <v>12.73</v>
+        <v>3.81</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>[14.41, 16.02, 13.5]</t>
+          <t>[5.81, 109.8, 32.3]</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>[14.4, 23.74, 14.3]</t>
+          <t>[5.8, 109.8, 36.4]</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4417,22 +4417,22 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>4.91</v>
+        <v>2.5</v>
       </c>
       <c r="G87" t="n">
-        <v>4</v>
+        <v>1.83</v>
       </c>
       <c r="H87" t="n">
-        <v>20.85</v>
+        <v>4.53</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>[16.02, 13.5, 10.73]</t>
+          <t>[109.8, 32.3, 59.0]</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>[23.74, 14.3, 14.2]</t>
+          <t>[109.8, 36.4, 60.4]</t>
         </is>
       </c>
     </row>
@@ -4444,12 +4444,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4463,22 +4463,22 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="G88" t="n">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="H88" t="n">
-        <v>10.87</v>
+        <v>6.54</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>[13.5, 10.73, 95.97]</t>
+          <t>[32.3, 59.0, 17.1]</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>[14.3, 14.2, 98.5]</t>
+          <t>[36.4, 60.4, 18.2]</t>
         </is>
       </c>
     </row>
@@ -4490,12 +4490,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4509,22 +4509,22 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>3.12</v>
+        <v>1.24</v>
       </c>
       <c r="G89" t="n">
-        <v>3.09</v>
+        <v>1.23</v>
       </c>
       <c r="H89" t="n">
-        <v>13.21</v>
+        <v>5.35</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>[10.73, 95.97, 22.63]</t>
+          <t>[59.0, 17.1, 14.4]</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>[14.2, 98.5, 25.9]</t>
+          <t>[60.4, 18.2, 15.6]</t>
         </is>
       </c>
     </row>
@@ -4536,12 +4536,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4555,22 +4555,22 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>2.72</v>
+        <v>2.51</v>
       </c>
       <c r="G90" t="n">
-        <v>2.68</v>
+        <v>2.11</v>
       </c>
       <c r="H90" t="n">
-        <v>7.3</v>
+        <v>11.41</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>[95.97, 22.63, 31.35]</t>
+          <t>[17.1, 14.4, 23.74]</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>[98.5, 25.9, 33.6]</t>
+          <t>[18.2, 15.6, 19.7]</t>
         </is>
       </c>
     </row>
@@ -4582,12 +4582,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4601,22 +4601,22 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>2.29</v>
+        <v>2.43</v>
       </c>
       <c r="G91" t="n">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="H91" t="n">
-        <v>6.5</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>[22.63, 31.35, 5.81]</t>
+          <t>[14.4, 23.74, 14.3]</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>[25.9, 33.6, 5.8]</t>
+          <t>[15.6, 19.7, 14.2]</t>
         </is>
       </c>
     </row>
@@ -4628,12 +4628,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4647,22 +4647,22 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>1.58</v>
+        <v>6.94</v>
       </c>
       <c r="G92" t="n">
-        <v>1.51</v>
+        <v>6.43</v>
       </c>
       <c r="H92" t="n">
-        <v>29.17</v>
+        <v>43.89</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>[3.64, 7.56, 7.36]</t>
+          <t>[2.75, 21.61, 7.55]</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>[2.4, 8.7, 9.5]</t>
+          <t>[6.4, 31.5, 13.3]</t>
         </is>
       </c>
     </row>
@@ -4674,12 +4674,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4689,26 +4689,26 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(0, 1, 2, 12)</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>1.4</v>
+        <v>6.91</v>
       </c>
       <c r="G93" t="n">
-        <v>1.13</v>
+        <v>5.64</v>
       </c>
       <c r="H93" t="n">
-        <v>13.98</v>
+        <v>32.1</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>[7.57, 7.36, 1.5]</t>
+          <t>[21.41, 6.88, 3.02]</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>[8.7, 9.5, 1.6]</t>
+          <t>[31.5, 13.3, 2.6]</t>
         </is>
       </c>
     </row>
@@ -4720,12 +4720,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -4735,26 +4735,26 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(0, 1, 2, 12)</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>1.24</v>
+        <v>3.85</v>
       </c>
       <c r="G94" t="n">
-        <v>0.75</v>
+        <v>2.85</v>
       </c>
       <c r="H94" t="n">
-        <v>9.640000000000001</v>
+        <v>24.54</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>[7.35, 1.5, 9.3]</t>
+          <t>[6.87, 3.02, 16.71]</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>[9.5, 1.6, 9.3]</t>
+          <t>[13.3, 2.6, 18.4]</t>
         </is>
       </c>
     </row>
@@ -4766,12 +4766,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -4781,26 +4781,26 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(0, 1, 2, 12)</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>2.43</v>
+        <v>1.24</v>
       </c>
       <c r="G95" t="n">
-        <v>1.44</v>
+        <v>1.12</v>
       </c>
       <c r="H95" t="n">
-        <v>4.52</v>
+        <v>25.2</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>[1.5, 9.3, 53.79]</t>
+          <t>[3.01, 16.72, 3.77]</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>[1.6, 9.3, 58.0]</t>
+          <t>[2.6, 18.4, 2.5]</t>
         </is>
       </c>
     </row>
@@ -4812,12 +4812,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -4827,26 +4827,26 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(0, 1, 2, 12)</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>2.43</v>
+        <v>1.62</v>
       </c>
       <c r="G96" t="n">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="H96" t="n">
-        <v>14.32</v>
+        <v>27.22</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>[9.31, 53.8, 0.81]</t>
+          <t>[16.72, 3.78, 6.85]</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>[9.3, 58.0, 0.6]</t>
+          <t>[18.4, 2.5, 8.7]</t>
         </is>
       </c>
     </row>
@@ -4858,12 +4858,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -4873,26 +4873,26 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(0, 1, 2, 12)</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>3.2</v>
+        <v>1.74</v>
       </c>
       <c r="G97" t="n">
-        <v>2.67</v>
+        <v>1.72</v>
       </c>
       <c r="H97" t="n">
-        <v>33.25</v>
+        <v>31.3</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>[53.81, 0.82, 2.78]</t>
+          <t>[3.8, 6.83, 7.71]</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>[58.0, 0.6, 6.4]</t>
+          <t>[2.5, 8.7, 9.7]</t>
         </is>
       </c>
     </row>
@@ -4904,12 +4904,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -4919,26 +4919,26 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(0, 1, 2, 12)</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>6.09</v>
+        <v>1.57</v>
       </c>
       <c r="G98" t="n">
-        <v>4.59</v>
+        <v>1.29</v>
       </c>
       <c r="H98" t="n">
-        <v>41.62</v>
+        <v>14.76</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>[0.82, 2.75, 21.6]</t>
+          <t>[6.85, 7.72, 1.66]</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>[0.6, 6.4, 31.5]</t>
+          <t>[8.7, 9.7, 1.7]</t>
         </is>
       </c>
     </row>
@@ -4950,12 +4950,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -4965,26 +4965,26 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(0, 1, 2, 12)</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>6.94</v>
+        <v>1.15</v>
       </c>
       <c r="G99" t="n">
-        <v>6.43</v>
+        <v>0.73</v>
       </c>
       <c r="H99" t="n">
-        <v>43.89</v>
+        <v>8.19</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>[2.75, 21.61, 7.55]</t>
+          <t>[7.71, 1.66, 9.76]</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>[6.4, 31.5, 13.3]</t>
+          <t>[9.7, 1.7, 9.6]</t>
         </is>
       </c>
     </row>
@@ -4996,12 +4996,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -5015,22 +5015,22 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>6.91</v>
+        <v>2.33</v>
       </c>
       <c r="G100" t="n">
-        <v>5.64</v>
+        <v>1.41</v>
       </c>
       <c r="H100" t="n">
-        <v>32.1</v>
+        <v>3.59</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>[21.41, 6.88, 3.02]</t>
+          <t>[1.66, 9.77, 55.89]</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>[31.5, 13.3, 2.6]</t>
+          <t>[1.7, 9.6, 59.92]</t>
         </is>
       </c>
     </row>
@@ -5042,12 +5042,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -5061,22 +5061,22 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>3.85</v>
+        <v>2.33</v>
       </c>
       <c r="G101" t="n">
-        <v>2.85</v>
+        <v>1.49</v>
       </c>
       <c r="H101" t="n">
-        <v>24.54</v>
+        <v>17.44</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>[6.87, 3.02, 16.71]</t>
+          <t>[9.78, 55.9, 0.86]</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>[13.3, 2.6, 18.4]</t>
+          <t>[9.6, 59.92, 0.6]</t>
         </is>
       </c>
     </row>
@@ -5088,12 +5088,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -5107,22 +5107,22 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>1.1</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G102" t="n">
-        <v>0.75</v>
+        <v>0.63</v>
       </c>
       <c r="H102" t="n">
-        <v>20.32</v>
+        <v>5.19460313115661e+22</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>[0.51, 0.0, 8.73]</t>
+          <t>[0.0, 7.97, 0.66]</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>[0.9, 0.0, 10.6]</t>
+          <t>[0.0, 9.2, 0.0]</t>
         </is>
       </c>
     </row>
@@ -5134,12 +5134,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -5153,22 +5153,22 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="G103" t="n">
-        <v>0.63</v>
+        <v>1.01</v>
       </c>
       <c r="H103" t="n">
-        <v>6.21</v>
+        <v>1.424580555665676e+23</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>[0.0, 8.73, 1.98]</t>
+          <t>[7.97, 0.66, 1.15]</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>[0.0, 10.6, 2.0]</t>
+          <t>[9.2, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -5180,12 +5180,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -5199,22 +5199,22 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>1.08</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="G104" t="n">
-        <v>0.63</v>
+        <v>5.8</v>
       </c>
       <c r="H104" t="n">
-        <v>6.21</v>
+        <v>1.369486280032197e+24</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>[8.73, 1.98, 6.2]</t>
+          <t>[0.66, 1.15, 15.59]</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>[10.6, 2.0, 6.2]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -5226,12 +5226,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -5245,22 +5245,22 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>0.23</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="G105" t="n">
-        <v>0.14</v>
+        <v>5.75</v>
       </c>
       <c r="H105" t="n">
-        <v>2.06</v>
+        <v>1.317540248720631e+24</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>[1.98, 6.2, 7.3]</t>
+          <t>[1.15, 15.59, 0.9]</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>[2.0, 6.2, 7.7]</t>
+          <t>[0.0, 0.0, 0.4]</t>
         </is>
       </c>
     </row>
@@ -5272,12 +5272,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -5287,26 +5287,26 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(2, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>0.23</v>
+        <v>2.84</v>
       </c>
       <c r="G106" t="n">
-        <v>0.13</v>
+        <v>1.69</v>
       </c>
       <c r="H106" t="n">
-        <v>1.73</v>
+        <v>3.873358128332551e+23</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>[6.2, 7.3, 0.0]</t>
+          <t>[4.92, 0.25, 0.0]</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>[6.2, 7.7, 0.0]</t>
+          <t>[0.0, 0.4, 0.0]</t>
         </is>
       </c>
     </row>
@@ -5318,17 +5318,17 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -5337,22 +5337,22 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>0.23</v>
+        <v>3.67</v>
       </c>
       <c r="G107" t="n">
-        <v>0.13</v>
+        <v>2.24</v>
       </c>
       <c r="H107" t="n">
-        <v>1.73</v>
+        <v>6.786512462876031e+16</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>[7.3, 0.0, 0.0]</t>
+          <t>[0.01, -0.0, 3.46]</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>[7.7, 0.0, 0.0]</t>
+          <t>[0.4, 0.0, 9.8]</t>
         </is>
       </c>
     </row>
@@ -5364,41 +5364,41 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(2, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>0.71</v>
+        <v>4.12</v>
       </c>
       <c r="G108" t="n">
-        <v>0.41</v>
+        <v>2.8</v>
       </c>
       <c r="H108" t="n">
-        <v>4.46</v>
+        <v>2.804932149157799e+17</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 7.97]</t>
+          <t>[0.0, 2.81, 0.58]</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 9.2]</t>
+          <t>[0.0, 9.8, 2.0]</t>
         </is>
       </c>
     </row>
@@ -5410,41 +5410,41 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(2, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>0.8100000000000001</v>
+        <v>5.16</v>
       </c>
       <c r="G109" t="n">
-        <v>0.63</v>
+        <v>4.5</v>
       </c>
       <c r="H109" t="n">
-        <v>5.19460313115661e+22</v>
+        <v>73.47</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>[0.0, 7.97, 0.66]</t>
+          <t>[2.18, 0.55, 1.88]</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>[0.0, 9.2, 0.0]</t>
+          <t>[9.8, 2.0, 6.3]</t>
         </is>
       </c>
     </row>
@@ -5456,41 +5456,41 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(2, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>1.04</v>
+        <v>3.58</v>
       </c>
       <c r="G110" t="n">
-        <v>1.01</v>
+        <v>3.28</v>
       </c>
       <c r="H110" t="n">
-        <v>1.424580555665676e+23</v>
+        <v>65.63</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>[7.97, 0.66, 1.15]</t>
+          <t>[0.77, 2.08, 2.02]</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>[9.2, 0.0, 0.0]</t>
+          <t>[2.0, 6.3, 6.4]</t>
         </is>
       </c>
     </row>
@@ -5502,41 +5502,41 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(2, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>9.029999999999999</v>
+        <v>3.27</v>
       </c>
       <c r="G111" t="n">
-        <v>5.8</v>
+        <v>2.67</v>
       </c>
       <c r="H111" t="n">
-        <v>1.369486280032197e+24</v>
+        <v>5.196984124422008e+16</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>[0.66, 1.15, 15.59]</t>
+          <t>[2.56, 2.13, -0.0]</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[6.3, 6.4, 0.0]</t>
         </is>
       </c>
     </row>
@@ -5548,12 +5548,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -5573,11 +5573,11 @@
         <v>0</v>
       </c>
       <c r="H112" t="n">
-        <v>6.547097770031115e+16</v>
+        <v>7.710133502615632e+19</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>[-0.0, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -5619,11 +5619,11 @@
         <v>0</v>
       </c>
       <c r="H113" t="n">
-        <v>3.119001150186468e+16</v>
+        <v>1.162348368514713e+20</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>[-0.0, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -5640,12 +5640,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -5659,13 +5659,13 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>0</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G114" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="H114" t="n">
-        <v>1.153850556826167e+16</v>
+        <v>1.769032783471131e+19</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, 1.2]</t>
         </is>
       </c>
     </row>
@@ -5686,12 +5686,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -5705,13 +5705,13 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>0</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G115" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="H115" t="n">
-        <v>1.695525523473752e+16</v>
+        <v>2.294604844176221e+19</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, 1.2, 0.0]</t>
         </is>
       </c>
     </row>
@@ -5732,17 +5732,17 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>(0, 0, 1)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -5751,22 +5751,22 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>0</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G116" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="H116" t="n">
-        <v>3.975831305464567e+19</v>
+        <v>1.739485037460374e+17</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.01, -0.0, 0.0]</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[1.2, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -5778,17 +5778,17 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>(0, 0, 1)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -5803,11 +5803,11 @@
         <v>0</v>
       </c>
       <c r="H117" t="n">
-        <v>4.056494360843017e+19</v>
+        <v>4.902388698314464e+18</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[-0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -5824,17 +5824,17 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>(0, 0, 1)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -5849,7 +5849,7 @@
         <v>0</v>
       </c>
       <c r="H118" t="n">
-        <v>1.065885357623999e+20</v>
+        <v>5.949865914647082e+18</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
@@ -5870,17 +5870,17 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>(0, 0, 1)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -5895,11 +5895,11 @@
         <v>0</v>
       </c>
       <c r="H119" t="n">
-        <v>7.710133502615632e+19</v>
+        <v>6.866844503559807e+18</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, -0.0]</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -5916,17 +5916,17 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>(0, 0, 1)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -5941,11 +5941,11 @@
         <v>0</v>
       </c>
       <c r="H120" t="n">
-        <v>1.162348368514713e+20</v>
+        <v>5.824967947506866e+19</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, -0.0, 0.0]</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -5962,17 +5962,17 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>(0, 0, 1)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -5981,22 +5981,22 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>0.6899999999999999</v>
+        <v>0</v>
       </c>
       <c r="G121" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="H121" t="n">
-        <v>1.769032783471131e+19</v>
+        <v>4.860970563751645e+19</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[-0.0, 0.0, -0.0]</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 1.2]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -6008,12 +6008,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -6023,26 +6023,26 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(0, 1, 2, 12)</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>25.49</v>
+        <v>10.67</v>
       </c>
       <c r="G122" t="n">
-        <v>20.5</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="H122" t="n">
-        <v>6.07</v>
+        <v>68.43000000000001</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>[367.31, 367.52, 334.51]</t>
+          <t>[0.67, 1.07, 23.39]</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>[369.4, 328.32, 354.71]</t>
+          <t>[3.82, 5.31, 41.1]</t>
         </is>
       </c>
     </row>
@@ -6054,12 +6054,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -6069,26 +6069,26 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(0, 1, 2, 12)</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>29.7</v>
+        <v>15.13</v>
       </c>
       <c r="G123" t="n">
-        <v>28.46</v>
+        <v>12.16</v>
       </c>
       <c r="H123" t="n">
-        <v>612.36</v>
+        <v>27.72</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>[368.34, 334.81, 26.87]</t>
+          <t>[2.37, 31.96, 416.45]</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>[328.32, 354.71, 1.4]</t>
+          <t>[5.31, 41.1, 440.84]</t>
         </is>
       </c>
     </row>
@@ -6100,12 +6100,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -6115,26 +6115,26 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(0, 1, 2, 12)</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>26.29</v>
+        <v>583.6</v>
       </c>
       <c r="G124" t="n">
-        <v>21.47</v>
+        <v>350.05</v>
       </c>
       <c r="H124" t="n">
-        <v>646.88</v>
+        <v>24.89</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>[316.45, 26.06, 2.39]</t>
+          <t>[44.53, 477.4, 730.62]</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>[354.71, 1.4, 0.89]</t>
+          <t>[41.1, 440.84, 1740.77]</t>
         </is>
       </c>
     </row>
@@ -6146,12 +6146,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -6161,26 +6161,26 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(0, 1, 2, 12)</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>15.1</v>
+        <v>592.6900000000001</v>
       </c>
       <c r="G125" t="n">
-        <v>9.630000000000001</v>
+        <v>383.67</v>
       </c>
       <c r="H125" t="n">
-        <v>697.53</v>
+        <v>29.24</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>[27.47, 2.45, 1.05]</t>
+          <t>[462.24, 720.24, 340.98]</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>[1.4, 0.89, 2.32]</t>
+          <t>[440.84, 1740.77, 450.07]</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -6207,26 +6207,26 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(0, 1, 2, 12)</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>1.18</v>
+        <v>602.97</v>
       </c>
       <c r="G126" t="n">
-        <v>1</v>
+        <v>409.27</v>
       </c>
       <c r="H126" t="n">
-        <v>53.27</v>
+        <v>35.25</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>[0.57, 0.49, 1.04]</t>
+          <t>[705.56, 337.94, 296.27]</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>[0.89, 2.32, 1.9]</t>
+          <t>[1740.77, 450.07, 376.72]</t>
         </is>
       </c>
     </row>
@@ -6238,12 +6238,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -6253,26 +6253,26 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(0, 1, 2, 12)</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>1.79</v>
+        <v>30.4</v>
       </c>
       <c r="G127" t="n">
-        <v>1.64</v>
+        <v>27.74</v>
       </c>
       <c r="H127" t="n">
-        <v>59.34</v>
+        <v>6.89</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>[0.61, 1.15, 1.35]</t>
+          <t>[491.07, 345.6, 324.21]</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>[2.32, 1.9, 3.82]</t>
+          <t>[450.07, 376.72, 335.32]</t>
         </is>
       </c>
     </row>
@@ -6284,12 +6284,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -6303,22 +6303,22 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>3</v>
+        <v>47.95</v>
       </c>
       <c r="G128" t="n">
-        <v>2.56</v>
+        <v>43.05</v>
       </c>
       <c r="H128" t="n">
-        <v>60.93</v>
+        <v>37.12</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>[2.36, 0.75, 1.14]</t>
+          <t>[332.6, 318.63, 3.85]</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>[1.9, 3.82, 5.31]</t>
+          <t>[376.72, 335.32, 72.2]</t>
         </is>
       </c>
     </row>
@@ -6330,12 +6330,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -6349,22 +6349,22 @@
         </is>
       </c>
       <c r="F129" t="n">
-        <v>10.67</v>
+        <v>39.41</v>
       </c>
       <c r="G129" t="n">
-        <v>8.369999999999999</v>
+        <v>22.91</v>
       </c>
       <c r="H129" t="n">
-        <v>68.43000000000001</v>
+        <v>36.17</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>[0.67, 1.07, 23.39]</t>
+          <t>[335.07, 3.93, 1.3]</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>[3.82, 5.31, 41.1]</t>
+          <t>[335.32, 72.2, 1.51]</t>
         </is>
       </c>
     </row>
@@ -6376,12 +6376,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -6395,22 +6395,22 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>15.13</v>
+        <v>51.24</v>
       </c>
       <c r="G130" t="n">
-        <v>12.16</v>
+        <v>41.73</v>
       </c>
       <c r="H130" t="n">
-        <v>27.72</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>[2.37, 31.96, 416.45]</t>
+          <t>[3.93, 1.3, 0.22]</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>[5.31, 41.1, 440.84]</t>
+          <t>[72.2, 1.51, 56.94]</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -6441,22 +6441,22 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>583.6</v>
+        <v>33.53</v>
       </c>
       <c r="G131" t="n">
-        <v>350.05</v>
+        <v>24.06</v>
       </c>
       <c r="H131" t="n">
-        <v>24.89</v>
+        <v>127.7</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>[44.53, 477.4, 730.62]</t>
+          <t>[4.38, 0.36, 0.86]</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>[41.1, 440.84, 1740.77]</t>
+          <t>[1.51, 56.94, 13.58]</t>
         </is>
       </c>
     </row>
@@ -6468,12 +6468,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -6487,22 +6487,22 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>17.82</v>
+        <v>168.3</v>
       </c>
       <c r="G132" t="n">
-        <v>11.7</v>
+        <v>140.29</v>
       </c>
       <c r="H132" t="n">
-        <v>9.32</v>
+        <v>26.31</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>[198.95, 304.36, 40.78]</t>
+          <t>[186.79, 713.57, 289.74]</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>[168.4, 304.5, 45.2]</t>
+          <t>[409.3, 901.6, 279.4]</t>
         </is>
       </c>
     </row>
@@ -6514,12 +6514,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -6529,26 +6529,26 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>131.37</v>
+        <v>124.28</v>
       </c>
       <c r="G133" t="n">
-        <v>77.66</v>
+        <v>89.88</v>
       </c>
       <c r="H133" t="n">
-        <v>26.14</v>
+        <v>14.13</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>[303.47, 40.74, 106.01]</t>
+          <t>[691.06, 297.37, 367.33]</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>[304.5, 45.2, 333.5]</t>
+          <t>[901.6, 279.4, 326.2]</t>
         </is>
       </c>
     </row>
@@ -6560,12 +6560,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -6575,26 +6575,26 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>131.67</v>
+        <v>274.23</v>
       </c>
       <c r="G134" t="n">
-        <v>83.26000000000001</v>
+        <v>177.84</v>
       </c>
       <c r="H134" t="n">
-        <v>30.18</v>
+        <v>23.63</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>[40.66, 106.18, 163.23]</t>
+          <t>[298.12, 368.26, 448.65]</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>[45.2, 333.5, 145.3]</t>
+          <t>[279.4, 326.2, 921.4]</t>
         </is>
       </c>
     </row>
@@ -6606,12 +6606,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -6621,26 +6621,26 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>131.7</v>
+        <v>274.34</v>
       </c>
       <c r="G135" t="n">
-        <v>84.79000000000001</v>
+        <v>177.16</v>
       </c>
       <c r="H135" t="n">
-        <v>27.81</v>
+        <v>24.77</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>[106.28, 163.3, 306.85]</t>
+          <t>[368.03, 448.37, 180.63]</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>[333.5, 145.3, 316.0]</t>
+          <t>[326.2, 921.4, 164.0]</t>
         </is>
       </c>
     </row>
@@ -6652,12 +6652,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -6667,26 +6667,26 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>15.66</v>
+        <v>310.46</v>
       </c>
       <c r="G136" t="n">
-        <v>12.52</v>
+        <v>248.07</v>
       </c>
       <c r="H136" t="n">
-        <v>7.73</v>
+        <v>35.07</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>[171.12, 310.18, 171.13]</t>
+          <t>[447.87, 180.42, 326.24]</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>[145.3, 316.0, 165.2]</t>
+          <t>[921.4, 164.0, 580.5]</t>
         </is>
       </c>
     </row>
@@ -6698,12 +6698,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -6713,26 +6713,26 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F137" t="n">
-        <v>129.14</v>
+        <v>150.06</v>
       </c>
       <c r="G137" t="n">
-        <v>78.39</v>
+        <v>110.18</v>
       </c>
       <c r="H137" t="n">
-        <v>20.01</v>
+        <v>36.56</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>[310.35, 171.18, 185.78]</t>
+          <t>[181.63, 328.43, 48.75]</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>[316.0, 165.2, 409.3]</t>
+          <t>[164.0, 580.5, 109.58]</t>
         </is>
       </c>
     </row>
@@ -6744,12 +6744,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -6759,26 +6759,26 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F138" t="n">
-        <v>168.15</v>
+        <v>214.05</v>
       </c>
       <c r="G138" t="n">
-        <v>138.69</v>
+        <v>192.64</v>
       </c>
       <c r="H138" t="n">
-        <v>26.26</v>
+        <v>126.17</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>[171.03, 186.24, 714.44]</t>
+          <t>[328.12, 48.71, 359.37]</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>[165.2, 409.3, 901.6]</t>
+          <t>[580.5, 109.58, 94.7]</t>
         </is>
       </c>
     </row>
@@ -6790,12 +6790,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -6805,26 +6805,26 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F139" t="n">
-        <v>168.3</v>
+        <v>158.12</v>
       </c>
       <c r="G139" t="n">
-        <v>140.29</v>
+        <v>114.74</v>
       </c>
       <c r="H139" t="n">
-        <v>26.31</v>
+        <v>115.52</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>[186.79, 713.57, 289.74]</t>
+          <t>[48.96, 361.24, 157.39]</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>[409.3, 901.6, 279.4]</t>
+          <t>[109.58, 94.7, 174.45]</t>
         </is>
       </c>
     </row>
@@ -6836,12 +6836,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -6851,26 +6851,26 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>124.28</v>
+        <v>33.57</v>
       </c>
       <c r="G140" t="n">
-        <v>89.88</v>
+        <v>27.69</v>
       </c>
       <c r="H140" t="n">
-        <v>14.13</v>
+        <v>22.47</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>[691.06, 297.37, 367.33]</t>
+          <t>[147.79, 181.91, 340.37]</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>[901.6, 279.4, 326.2]</t>
+          <t>[94.7, 174.45, 317.85]</t>
         </is>
       </c>
     </row>
@@ -6882,12 +6882,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -6897,26 +6897,26 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F141" t="n">
-        <v>274.23</v>
+        <v>16.17</v>
       </c>
       <c r="G141" t="n">
-        <v>177.84</v>
+        <v>15.69</v>
       </c>
       <c r="H141" t="n">
-        <v>23.63</v>
+        <v>7.75</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>[298.12, 368.26, 448.65]</t>
+          <t>[184.78, 335.02, 183.35]</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>[279.4, 326.2, 921.4]</t>
+          <t>[174.45, 317.85, 163.8]</t>
         </is>
       </c>
     </row>
@@ -6928,12 +6928,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -6943,17 +6943,17 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(1, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G142" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="H142" t="n">
-        <v>1.343496320556022e+19</v>
+        <v>240371627716.67</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
@@ -6962,7 +6962,7 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, 0.7]</t>
         </is>
       </c>
     </row>
@@ -6974,12 +6974,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -6989,26 +6989,26 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(1, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="G143" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="H143" t="n">
-        <v>1.092401066543267e+19</v>
+        <v>73543496383.33</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, -0.0]</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, 0.7, 1.4]</t>
         </is>
       </c>
     </row>
@@ -7020,12 +7020,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -7035,26 +7035,26 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>0</v>
+        <v>8.76</v>
       </c>
       <c r="G144" t="n">
-        <v>0</v>
+        <v>5.73</v>
       </c>
       <c r="H144" t="n">
-        <v>9.052032029192716e+18</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, 2.0]</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.7, 1.4, 17.1]</t>
         </is>
       </c>
     </row>
@@ -7066,12 +7066,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -7081,26 +7081,26 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>0.97</v>
+        <v>9.27</v>
       </c>
       <c r="G145" t="n">
-        <v>0.5600000000000001</v>
+        <v>7.25</v>
       </c>
       <c r="H145" t="n">
-        <v>5.082778453803211e+18</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, 2.0, 0.0]</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 1.68]</t>
+          <t>[1.4, 17.1, 5.25]</t>
         </is>
       </c>
     </row>
@@ -7112,12 +7112,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -7127,26 +7127,26 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>0.97</v>
+        <v>5.73</v>
       </c>
       <c r="G146" t="n">
-        <v>0.5600000000000001</v>
+        <v>4.98</v>
       </c>
       <c r="H146" t="n">
-        <v>4.342041167115786e+18</v>
+        <v>82.84999999999999</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[8.8, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>[0.0, 1.68, 0.0]</t>
+          <t>[17.1, 5.25, 1.4]</t>
         </is>
       </c>
     </row>
@@ -7158,41 +7158,41 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>(1, 0, 2)</t>
+          <t>(0, 0, 0)</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>2.09</v>
+        <v>3.14</v>
       </c>
       <c r="G147" t="n">
-        <v>1.21</v>
+        <v>2.22</v>
       </c>
       <c r="H147" t="n">
-        <v>71.83</v>
+        <v>66.67</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>[5.3, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>[1.68, 0.0, 0.0]</t>
+          <t>[5.25, 1.4, 0.0]</t>
         </is>
       </c>
     </row>
@@ -7204,17 +7204,17 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -7223,22 +7223,22 @@
         </is>
       </c>
       <c r="F148" t="n">
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="G148" t="n">
-        <v>0</v>
+        <v>0.58</v>
       </c>
       <c r="H148" t="n">
-        <v>0</v>
+        <v>1.7454572265553e+21</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.02, 0.02, 0.02]</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[1.4, 0.0, 0.35]</t>
         </is>
       </c>
     </row>
@@ -7250,41 +7250,41 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>(1, 1, 1, 12)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>0.4</v>
+        <v>0.18</v>
       </c>
       <c r="G149" t="n">
-        <v>0.23</v>
+        <v>0.18</v>
       </c>
       <c r="H149" t="n">
-        <v>240371627716.67</v>
+        <v>2.755327549940556e+22</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.18, 0.18, 0.18]</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.7]</t>
+          <t>[0.0, 0.35, 0.0]</t>
         </is>
       </c>
     </row>
@@ -7296,41 +7296,41 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>(1, 1, 1, 12)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>0.9</v>
+        <v>1228.73</v>
       </c>
       <c r="G150" t="n">
-        <v>0.7</v>
+        <v>709.52</v>
       </c>
       <c r="H150" t="n">
-        <v>73543496383.33</v>
+        <v>9.981259535799425e+19</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, -0.0]</t>
+          <t>[0.0, 0.0, 2132.2]</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>[0.0, 0.7, 1.4]</t>
+          <t>[0.35, 0.0, 3.98]</t>
         </is>
       </c>
     </row>
@@ -7342,17 +7342,17 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -7361,22 +7361,22 @@
         </is>
       </c>
       <c r="F151" t="n">
-        <v>8.76</v>
+        <v>8326.280000000001</v>
       </c>
       <c r="G151" t="n">
-        <v>5.73</v>
+        <v>4807.19</v>
       </c>
       <c r="H151" t="n">
-        <v>96.09999999999999</v>
+        <v>1.351481259258717e+21</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 2.0]</t>
+          <t>[0.01, 14425.53, 0.01]</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>[0.7, 1.4, 17.1]</t>
+          <t>[0.0, 3.98, 0.0]</t>
         </is>
       </c>
     </row>
@@ -7388,41 +7388,41 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>(3, 0, 0)</t>
+          <t>(0, 0, 0)</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>7.35</v>
+        <v>23.47</v>
       </c>
       <c r="G152" t="n">
-        <v>4.26</v>
+        <v>16.21</v>
       </c>
       <c r="H152" t="n">
-        <v>7541468423197755</v>
+        <v>7.407370299653958e+17</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>[-0.0, 0.26, 0.06]</t>
+          <t>[43.94, 10.2, 0.0]</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>[0.0, 0.3, 12.8]</t>
+          <t>[4.3, 1.2, 0.0]</t>
         </is>
       </c>
     </row>
@@ -7434,41 +7434,41 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>(3, 0, 0)</t>
+          <t>(0, 0, 0)</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>7.35</v>
+        <v>13.09</v>
       </c>
       <c r="G153" t="n">
-        <v>4.26</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="H153" t="n">
-        <v>2.298537184543735e+17</v>
+        <v>6.231184011707407e+17</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>[0.27, 0.06, 0.0]</t>
+          <t>[8.74, 0.0, 24.08]</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>[0.3, 12.8, 0.0]</t>
+          <t>[1.2, 0.0, 2.7]</t>
         </is>
       </c>
     </row>
@@ -7480,41 +7480,41 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>(3, 0, 0)</t>
+          <t>(0, 0, 0)</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>7.35</v>
+        <v>14.26</v>
       </c>
       <c r="G154" t="n">
-        <v>4.28</v>
+        <v>11.62</v>
       </c>
       <c r="H154" t="n">
-        <v>7.918742106388837e+21</v>
+        <v>5.412157761450385e+17</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>[0.06, 0.0, 0.1]</t>
+          <t>[0.0, 21.27, 18.19]</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>[12.8, 0.0, 0.0]</t>
+          <t>[0.0, 2.7, 1.9]</t>
         </is>
       </c>
     </row>
@@ -7526,41 +7526,41 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>(3, 0, 0)</t>
+          <t>(0, 0, 0)</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>21.54</v>
+        <v>12.41</v>
       </c>
       <c r="G155" t="n">
-        <v>12.46</v>
+        <v>10.12</v>
       </c>
       <c r="H155" t="n">
-        <v>5.273532248886106e+21</v>
+        <v>4.703437204316282e+17</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>[-0.0, 0.07, 0.5]</t>
+          <t>[18.84, 16.11, 0.0]</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 37.8]</t>
+          <t>[2.7, 1.9, 0.0]</t>
         </is>
       </c>
     </row>
@@ -7572,41 +7572,41 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>(3, 0, 0)</t>
+          <t>(0, 0, 0)</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>21.53</v>
+        <v>7.31</v>
       </c>
       <c r="G156" t="n">
-        <v>12.45</v>
+        <v>4.68</v>
       </c>
       <c r="H156" t="n">
-        <v>5.288561481563219e+21</v>
+        <v>4.141781060260817e+17</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>[0.07, 0.51, 0.0]</t>
+          <t>[14.47, 0.0, 1.88]</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>[0.0, 37.8, 0.0]</t>
+          <t>[1.9, 0.0, 0.4]</t>
         </is>
       </c>
     </row>
@@ -7618,41 +7618,41 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(2, 1, 1)</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F157" t="n">
-        <v>209.74</v>
+        <v>108510.35</v>
       </c>
       <c r="G157" t="n">
-        <v>139.08</v>
+        <v>62648.65</v>
       </c>
       <c r="H157" t="n">
-        <v>1.096978975942635e+18</v>
+        <v>3.129622455820301e+16</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>[396.3, 0.0, 63.04]</t>
+          <t>[0.0, 187945.85, 0.59]</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>[37.8, 0.0, 4.3]</t>
+          <t>[0.0, 0.4, 1.1]</t>
         </is>
       </c>
     </row>
@@ -7664,41 +7664,41 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(2, 1, 1)</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>28.61</v>
+        <v>108080.44</v>
       </c>
       <c r="G158" t="n">
-        <v>19.78</v>
+        <v>62400.44</v>
       </c>
       <c r="H158" t="n">
-        <v>9.02564639697742e+17</v>
+        <v>1.747991133468885e+16</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>[0.0, 52.61, 12.22]</t>
+          <t>[187201.21, 0.58, 0.0]</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>[0.0, 4.3, 1.2]</t>
+          <t>[0.4, 1.1, 0.0]</t>
         </is>
       </c>
     </row>
@@ -7710,17 +7710,17 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(2, 1, 0)</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -7729,22 +7729,22 @@
         </is>
       </c>
       <c r="F159" t="n">
-        <v>23.47</v>
+        <v>5.67</v>
       </c>
       <c r="G159" t="n">
-        <v>16.21</v>
+        <v>3.27</v>
       </c>
       <c r="H159" t="n">
-        <v>7.407370299653958e+17</v>
+        <v>2.23451483827651e+16</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>[43.94, 10.2, 0.0]</t>
+          <t>[10.92, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>[4.3, 1.2, 0.0]</t>
+          <t>[1.1, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -7756,17 +7756,17 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(0, 1, 2)</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -7775,22 +7775,22 @@
         </is>
       </c>
       <c r="F160" t="n">
-        <v>13.09</v>
+        <v>7.36</v>
       </c>
       <c r="G160" t="n">
-        <v>9.640000000000001</v>
+        <v>4.25</v>
       </c>
       <c r="H160" t="n">
-        <v>6.231184011707407e+17</v>
+        <v>7.628261915048605e+16</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>[8.74, 0.0, 24.08]</t>
+          <t>[0.0, -0.0, 15.55]</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>[1.2, 0.0, 2.7]</t>
+          <t>[0.0, 0.0, 28.3]</t>
         </is>
       </c>
     </row>
@@ -7802,17 +7802,17 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(0, 1, 2)</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -7821,22 +7821,22 @@
         </is>
       </c>
       <c r="F161" t="n">
-        <v>14.26</v>
+        <v>8.42</v>
       </c>
       <c r="G161" t="n">
-        <v>11.62</v>
+        <v>4.86</v>
       </c>
       <c r="H161" t="n">
-        <v>5.412157761450385e+17</v>
+        <v>9.47624765418523e+16</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>[0.0, 21.27, 18.19]</t>
+          <t>[-0.0, 13.71, -0.0]</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>[0.0, 2.7, 1.9]</t>
+          <t>[0.0, 28.3, 0.0]</t>
         </is>
       </c>
     </row>
@@ -7848,12 +7848,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F162" t="n">
@@ -7873,7 +7873,7 @@
         <v>0</v>
       </c>
       <c r="H162" t="n">
-        <v>2.294409817119985e+17</v>
+        <v>0</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
@@ -7894,12 +7894,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -7909,7 +7909,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F163" t="n">
@@ -7919,7 +7919,7 @@
         <v>0</v>
       </c>
       <c r="H163" t="n">
-        <v>2.13902640228998e+17</v>
+        <v>0</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
@@ -7940,12 +7940,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -7955,7 +7955,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F164" t="n">
@@ -7965,7 +7965,7 @@
         <v>0</v>
       </c>
       <c r="H164" t="n">
-        <v>2.002914867209989e+17</v>
+        <v>150</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
@@ -7986,12 +7986,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F165" t="n">
@@ -8011,7 +8011,7 @@
         <v>0</v>
       </c>
       <c r="H165" t="n">
-        <v>1.882752817579816e+17</v>
+        <v>0</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
@@ -8032,12 +8032,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -8047,7 +8047,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F166" t="n">
@@ -8057,7 +8057,7 @@
         <v>0</v>
       </c>
       <c r="H166" t="n">
-        <v>1.775931490377406e+17</v>
+        <v>0</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
@@ -8078,12 +8078,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -8124,12 +8124,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -8139,7 +8139,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>(1, 1, 1, 12)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F168" t="n">
@@ -8149,11 +8149,11 @@
         <v>0</v>
       </c>
       <c r="H168" t="n">
-        <v>34570019842050</v>
+        <v>0</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>[-0.0, -0.0, -0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -8170,12 +8170,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -8216,12 +8216,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -8262,12 +8262,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -8287,7 +8287,7 @@
         <v>0</v>
       </c>
       <c r="H171" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
@@ -8308,12 +8308,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -8327,22 +8327,22 @@
         </is>
       </c>
       <c r="F172" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="G172" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="H172" t="n">
-        <v>7.943553072589201e+17</v>
+        <v>1.222338818120332e+17</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>[0.0, -0.0, -0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>[0.0, 0.42, 0.0]</t>
+          <t>[0.4, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -8354,12 +8354,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -8373,22 +8373,22 @@
         </is>
       </c>
       <c r="F173" t="n">
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="G173" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="H173" t="n">
-        <v>1.560432496023018e+18</v>
+        <v>1.017292212223602e+19</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>[-0.0, -0.0, 0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>[0.42, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -8400,12 +8400,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -8425,7 +8425,7 @@
         <v>0</v>
       </c>
       <c r="H174" t="n">
-        <v>2.845332828021604e+18</v>
+        <v>1.239213659150356e+19</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -8471,7 +8471,7 @@
         <v>0</v>
       </c>
       <c r="H175" t="n">
-        <v>2.78669471418722e+18</v>
+        <v>1.313976004290192e+19</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
@@ -8492,12 +8492,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -8517,7 +8517,7 @@
         <v>0</v>
       </c>
       <c r="H176" t="n">
-        <v>2.04837677282003e+17</v>
+        <v>6.845694913800647e+18</v>
       </c>
       <c r="I176" t="inlineStr">
         <is>
@@ -8538,12 +8538,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -8557,22 +8557,22 @@
         </is>
       </c>
       <c r="F177" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="G177" t="n">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="H177" t="n">
-        <v>5.370702858136843e+16</v>
+        <v>9.587535239768378e+17</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, -0.0]</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.4]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -8584,12 +8584,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -8603,22 +8603,22 @@
         </is>
       </c>
       <c r="F178" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="G178" t="n">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="H178" t="n">
-        <v>1.189793585084016e+17</v>
+        <v>1.686362664316225e+18</v>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, -0.0, 0.0]</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>[0.0, 0.4, 0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -8630,12 +8630,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -8649,22 +8649,22 @@
         </is>
       </c>
       <c r="F179" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="G179" t="n">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="H179" t="n">
-        <v>1.222338818120332e+17</v>
+        <v>1.615195116408925e+18</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[-0.0, 0.0, -0.0]</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>[0.4, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -8676,12 +8676,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -8701,11 +8701,11 @@
         <v>0</v>
       </c>
       <c r="H180" t="n">
-        <v>1.017292212223602e+19</v>
+        <v>1.74086988936562e+18</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, -0.0, -0.0]</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -8722,12 +8722,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -8747,11 +8747,11 @@
         <v>0</v>
       </c>
       <c r="H181" t="n">
-        <v>1.239213659150356e+19</v>
+        <v>1.108955772086276e+17</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[-0.0, -0.0, -0.0]</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -8793,11 +8793,11 @@
         <v>0</v>
       </c>
       <c r="H182" t="n">
-        <v>133.33</v>
+        <v>1.006088480506221e+19</v>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>[0.0, -0.0, 0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -8814,12 +8814,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -8839,7 +8839,7 @@
         <v>0</v>
       </c>
       <c r="H183" t="n">
-        <v>0</v>
+        <v>1.017632714765946e+19</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
@@ -8860,12 +8860,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -8885,7 +8885,7 @@
         <v>0</v>
       </c>
       <c r="H184" t="n">
-        <v>0</v>
+        <v>3.615353804383641e+18</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -8906,12 +8906,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -8931,7 +8931,7 @@
         <v>0</v>
       </c>
       <c r="H185" t="n">
-        <v>0</v>
+        <v>3.643132735013318e+18</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
@@ -8952,12 +8952,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -8977,7 +8977,7 @@
         <v>0</v>
       </c>
       <c r="H186" t="n">
-        <v>1.566152469914927e+19</v>
+        <v>3.670698876039837e+18</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
@@ -8998,12 +8998,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -9023,7 +9023,7 @@
         <v>0</v>
       </c>
       <c r="H187" t="n">
-        <v>1.589984739909201e+19</v>
+        <v>0</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
@@ -9044,12 +9044,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -9069,7 +9069,7 @@
         <v>0</v>
       </c>
       <c r="H188" t="n">
-        <v>4.013923797190577e+19</v>
+        <v>0</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
@@ -9090,12 +9090,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -9115,7 +9115,7 @@
         <v>0</v>
       </c>
       <c r="H189" t="n">
-        <v>1.006088480506221e+19</v>
+        <v>0</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
@@ -9136,12 +9136,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -9161,7 +9161,7 @@
         <v>0</v>
       </c>
       <c r="H190" t="n">
-        <v>1.017632714765946e+19</v>
+        <v>0</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
@@ -9182,12 +9182,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -9207,11 +9207,11 @@
         <v>0</v>
       </c>
       <c r="H191" t="n">
-        <v>3.615353804383641e+18</v>
+        <v>133.33</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, -0.0]</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -9228,17 +9228,17 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>(1, 1, 1)</t>
+          <t>(0, 1, 2)</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -9247,22 +9247,22 @@
         </is>
       </c>
       <c r="F192" t="n">
-        <v>6.67</v>
+        <v>26.61</v>
       </c>
       <c r="G192" t="n">
-        <v>5.66</v>
+        <v>26.24</v>
       </c>
       <c r="H192" t="n">
-        <v>9.24</v>
+        <v>18.87</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>[71.88, 65.91, 90.98]</t>
+          <t>[173.63, 111.81, 114.51]</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>[67.86, 55.34, 88.6]</t>
+          <t>[142.22, 138.52, 135.1]</t>
         </is>
       </c>
     </row>
@@ -9274,41 +9274,41 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>(0, 1, 2)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F193" t="n">
-        <v>14.26</v>
+        <v>48.06</v>
       </c>
       <c r="G193" t="n">
-        <v>10.92</v>
+        <v>45.76</v>
       </c>
       <c r="H193" t="n">
-        <v>13.16</v>
+        <v>25.7</v>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>[64.94, 88.2, 82.18]</t>
+          <t>[102.01, 100.79, 195.71]</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>[55.34, 88.6, 104.94]</t>
+          <t>[138.52, 135.1, 262.18]</t>
         </is>
       </c>
     </row>
@@ -9320,12 +9320,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -9335,26 +9335,26 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F194" t="n">
-        <v>17.47</v>
+        <v>257.97</v>
       </c>
       <c r="G194" t="n">
-        <v>13.81</v>
+        <v>172.4</v>
       </c>
       <c r="H194" t="n">
-        <v>13.58</v>
+        <v>31.84</v>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>[88.35, 78.53, 81.85]</t>
+          <t>[108.92, 214.69, 320.92]</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>[88.6, 104.94, 96.62]</t>
+          <t>[135.1, 262.18, 764.44]</t>
         </is>
       </c>
     </row>
@@ -9366,12 +9366,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -9381,26 +9381,26 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F195" t="n">
-        <v>24.05</v>
+        <v>245.28</v>
       </c>
       <c r="G195" t="n">
-        <v>23.26</v>
+        <v>156.09</v>
       </c>
       <c r="H195" t="n">
-        <v>22.72</v>
+        <v>24.29</v>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>[78.52, 81.91, 74.55]</t>
+          <t>[216.36, 342.08, 69.11]</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>[104.94, 96.62, 103.21]</t>
+          <t>[262.18, 764.44, 69.2]</t>
         </is>
       </c>
     </row>
@@ -9412,41 +9412,41 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>(0, 1, 2)</t>
+          <t>(1, 1, 2)</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F196" t="n">
-        <v>13.86</v>
+        <v>228.12</v>
       </c>
       <c r="G196" t="n">
-        <v>12.17</v>
+        <v>135.93</v>
       </c>
       <c r="H196" t="n">
-        <v>14.12</v>
+        <v>23.72</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>[84.0, 83.14, 35.05]</t>
+          <t>[369.43, 77.34, 64.77]</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>[96.62, 103.21, 38.88]</t>
+          <t>[764.44, 69.2, 60.13]</t>
         </is>
       </c>
     </row>
@@ -9458,41 +9458,41 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>(0, 1, 2)</t>
+          <t>(3, 0, 0)</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F197" t="n">
-        <v>15.65</v>
+        <v>20.83</v>
       </c>
       <c r="G197" t="n">
-        <v>13.5</v>
+        <v>19.61</v>
       </c>
       <c r="H197" t="n">
-        <v>12.62</v>
+        <v>25.83</v>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>[84.08, 36.58, 161.28]</t>
+          <t>[82.9, 75.78, 122.57]</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>[103.21, 38.88, 142.22]</t>
+          <t>[69.2, 60.13, 93.1]</t>
         </is>
       </c>
     </row>
@@ -9504,41 +9504,41 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>(0, 1, 2)</t>
+          <t>(3, 0, 0)</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F198" t="n">
-        <v>23.78</v>
+        <v>24.32</v>
       </c>
       <c r="G198" t="n">
-        <v>19.9</v>
+        <v>23.09</v>
       </c>
       <c r="H198" t="n">
-        <v>15.11</v>
+        <v>28.62</v>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>[37.36, 172.22, 110.35]</t>
+          <t>[74.49, 115.01, 118.79]</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>[38.88, 142.22, 138.52]</t>
+          <t>[60.13, 93.1, 85.8]</t>
         </is>
       </c>
     </row>
@@ -9550,41 +9550,41 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>(0, 1, 2)</t>
+          <t>(2, 0, 2)</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F199" t="n">
-        <v>26.61</v>
+        <v>37.03</v>
       </c>
       <c r="G199" t="n">
-        <v>26.24</v>
+        <v>34.84</v>
       </c>
       <c r="H199" t="n">
-        <v>18.87</v>
+        <v>38.63</v>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>[173.63, 111.81, 114.51]</t>
+          <t>[116.25, 138.04, 125.73]</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>[142.22, 138.52, 135.1]</t>
+          <t>[93.1, 85.8, 96.61]</t>
         </is>
       </c>
     </row>
@@ -9596,17 +9596,17 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(3, 0, 0)</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -9615,22 +9615,22 @@
         </is>
       </c>
       <c r="F200" t="n">
-        <v>48.06</v>
+        <v>13.17</v>
       </c>
       <c r="G200" t="n">
-        <v>45.76</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="H200" t="n">
-        <v>25.7</v>
+        <v>10.14</v>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>[102.01, 100.79, 195.71]</t>
+          <t>[108.35, 100.02, 105.64]</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>[138.52, 135.1, 262.18]</t>
+          <t>[85.8, 96.61, 105.0]</t>
         </is>
       </c>
     </row>
@@ -9642,41 +9642,41 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>(0, 1, 2)</t>
+          <t>(3, 0, 0)</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F201" t="n">
-        <v>257.97</v>
+        <v>5.24</v>
       </c>
       <c r="G201" t="n">
-        <v>172.4</v>
+        <v>4.41</v>
       </c>
       <c r="H201" t="n">
-        <v>31.84</v>
+        <v>7.28</v>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>[108.92, 214.69, 320.92]</t>
+          <t>[97.08, 99.25, 37.09]</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>[135.1, 262.18, 764.44]</t>
+          <t>[96.61, 105.0, 44.1]</t>
         </is>
       </c>
     </row>
